--- a/docs/language-review/es-latam/template/es-latam-interface-review-v3.2.0.xlsx
+++ b/docs/language-review/es-latam/template/es-latam-interface-review-v3.2.0.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="LÉEME" sheetId="1" state="visible" r:id="rId3"/>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">• La pestaña 2-Decisiones recoge decisiones que tomamos a propósito y sobre las que necesitamos tu opinión explícita. Son pocas filas y valen mucho.</t>
   </si>
   <si>
-    <t xml:space="preserve">• La pestaña 8-Muestra-contenido es una MUESTRA (unas 40 preguntas por idioma, de unas 0 en total). Sirve para detectar problemas sistemáticos. Si ves un patrón que se repite, dilo en la nota: lo arreglamos en todo el corpus, no solo en esa fila.</t>
+    <t xml:space="preserve">• Este paquete es SOLO de interfaz: no trae ninguna muestra del contenido de los cursos. El español que la app enseña y el español que explica otros idiomas se revisan en los otros dos paquetes. Lo que sí te pedimos aquí: si ves un motivo que se repite —una fórmula, una elección de término, una regla tipográfica—, señálalo UNA vez en la nota y lo aplicamos a todo el corpus, no solo a la fila donde lo viste.</t>
   </si>
   <si>
     <t xml:space="preserve">Al terminar</t>
@@ -2927,19 +2927,19 @@
     <t xml:space="preserve">Una nota de la versión 2.13.0 dice «Cuatro idiomas nuevos» pero enumera tres. El error viene del inglés original y lo tradujimos igual, a propósito.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pestaña 9 — v2.13.0, primera viñeta</t>
+    <t xml:space="preserve">Pestaña 8-Novedades — v2.13.0, primera viñeta</t>
   </si>
   <si>
     <t xml:space="preserve">DEC-16</t>
   </si>
   <si>
-    <t xml:space="preserve">Muestra de contenido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La pestaña 8 es una muestra de 400 preguntas de unas 14.000. Buscamos problemas SISTEMÁTICOS, no una revisión exhaustiva.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Si algo se repite (por ejemplo una fórmula de explicación que suena rara), señálalo una vez y lo arreglamos en todo el corpus.</t>
+    <t xml:space="preserve">El contenido de los cursos no está en este paquete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Este paquete no trae ninguna muestra de contenido: solo cubre la interfaz. El español de los cursos se revisa en los otros dos paquetes — 665 preguntas del curso de español y 609 entradas del Banco de Palabras en «contenido enseñado»; 1.548 preguntas, 2.768 glosas y una muestra de 400 filas de unas 13.974 en «explicaciones». Lo que te pedimos aquí es que señales cualquier motivo que se repita: una fórmula, una elección de término, una regla tipográfica.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Señala el motivo UNA vez en la nota; nosotros lo propagamos a todo el corpus.</t>
   </si>
   <si>
     <t xml:space="preserve">Sección</t>
@@ -13422,7 +13422,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="2" t="s">
         <v>34</v>
       </c>
